--- a/data/gravel/Pinarello Granger X 2025.xlsx
+++ b/data/gravel/Pinarello Granger X 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B3C055F-00D5-D446-8085-A6D39F7C589F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D20CEE4-71AB-9D40-BEFE-C6E2C9DB4BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29700" yWindow="-23660" windowWidth="29220" windowHeight="18480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1880" yWindow="500" windowWidth="27360" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -257,9 +257,6 @@
     <t>L</t>
   </si>
   <si>
-    <t>a8:i32</t>
-  </si>
-  <si>
     <t>Pinarello</t>
   </si>
   <si>
@@ -327,6 +324,9 @@
   </si>
   <si>
     <t>G - axle_crown</t>
+  </si>
+  <si>
+    <t>a8:h31</t>
   </si>
 </sst>
 </file>
@@ -708,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
@@ -716,7 +716,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
@@ -740,7 +740,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
@@ -748,7 +748,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -756,7 +756,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C8" s="1">
         <v>470</v>
@@ -777,37 +777,37 @@
         <v>600</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>73</v>
       </c>
       <c r="L8" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="N8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="O8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="R8" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="S8" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="S8" s="1" t="s">
+      <c r="T8" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.3">
@@ -815,7 +815,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C9" s="1">
         <v>522</v>
@@ -874,7 +874,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C10" s="1">
         <v>74.5</v>
@@ -933,7 +933,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C11" s="1">
         <v>69.75</v>
@@ -992,7 +992,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1">
         <v>430</v>
@@ -1051,7 +1051,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C13" s="1">
         <v>125</v>
@@ -1110,7 +1110,7 @@
         <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C14" s="1">
         <v>72</v>
@@ -1169,7 +1169,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" s="1">
         <v>50</v>
@@ -1195,7 +1195,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C16" s="1">
         <v>395</v>
@@ -1221,7 +1221,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C17" s="1">
         <v>363</v>
@@ -1247,7 +1247,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C18" s="1">
         <v>543.4</v>
@@ -1362,6 +1362,24 @@
       <c r="B28" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="C28" s="1">
+        <v>50</v>
+      </c>
+      <c r="D28" s="1">
+        <v>50</v>
+      </c>
+      <c r="E28" s="1">
+        <v>50</v>
+      </c>
+      <c r="F28" s="1">
+        <v>50</v>
+      </c>
+      <c r="G28" s="1">
+        <v>50</v>
+      </c>
+      <c r="H28" s="1">
+        <v>50</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
@@ -1369,6 +1387,24 @@
       </c>
       <c r="B29" s="1" t="s">
         <v>26</v>
+      </c>
+      <c r="C29" s="1">
+        <v>50</v>
+      </c>
+      <c r="D29" s="1">
+        <v>50</v>
+      </c>
+      <c r="E29" s="1">
+        <v>50</v>
+      </c>
+      <c r="F29" s="1">
+        <v>50</v>
+      </c>
+      <c r="G29" s="1">
+        <v>50</v>
+      </c>
+      <c r="H29" s="1">
+        <v>50</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
@@ -1446,7 +1482,7 @@
         <v>31</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
@@ -1465,11 +1501,17 @@
       <c r="A40" s="1" t="s">
         <v>34</v>
       </c>
+      <c r="B40" s="1">
+        <v>50</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>35</v>
       </c>
+      <c r="B41" s="1">
+        <v>2.2000000000000002</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
@@ -1579,15 +1621,24 @@
       <c r="A61" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="B61" s="1">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="B62" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>57</v>
+      </c>
+      <c r="B63" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">

--- a/data/gravel/Pinarello Granger X 2025.xlsx
+++ b/data/gravel/Pinarello Granger X 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D20CEE4-71AB-9D40-BEFE-C6E2C9DB4BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63729BE0-AB57-5646-8250-32CCD87B8F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1880" yWindow="500" windowWidth="27360" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="500" windowWidth="27360" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="99">
   <si>
     <t>brand</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>a8:h31</t>
+  </si>
+  <si>
+    <t>https://pinarello.com/storage/Variant/12a67795e58ed5c19e2b3ddc2ba9c2d2.png</t>
   </si>
 </sst>
 </file>
@@ -743,6 +746,11 @@
         <v>76</v>
       </c>
     </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>

--- a/data/gravel/Pinarello Granger X 2025.xlsx
+++ b/data/gravel/Pinarello Granger X 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63729BE0-AB57-5646-8250-32CCD87B8F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10A4EA2-DA01-BD44-901E-01BF661A0EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="500" windowWidth="27360" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="101">
   <si>
     <t>brand</t>
   </si>
@@ -330,6 +330,12 @@
   </si>
   <si>
     <t>https://pinarello.com/storage/Variant/12a67795e58ed5c19e2b3ddc2ba9c2d2.png</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Treviso, Italy</t>
   </si>
 </sst>
 </file>
@@ -699,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T71"/>
+  <dimension ref="A1:T72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1654,39 +1660,47 @@
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Pinarello Granger X 2025.xlsx
+++ b/data/gravel/Pinarello Granger X 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10A4EA2-DA01-BD44-901E-01BF661A0EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2649C62-F4D5-1B47-8D96-6B390F00D5C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="500" windowWidth="27360" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -336,6 +336,24 @@
   </si>
   <si>
     <t>Treviso, Italy</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -705,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T72"/>
+  <dimension ref="A1:T78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1565,141 +1583,171 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>42</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B50" s="1">
-        <v>27.2</v>
+        <v>103</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B56" s="1">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B67" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B68" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B69" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>100</v>
       </c>
     </row>
